--- a/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T11:00:33+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2062,7 +2062,7 @@
     <t>Code for time period of occurrence</t>
   </si>
   <si>
-    <t>Hier werden Tageszeiten angegeben, zu denen das Arzneimittel verabreicht/eingenommen wird.
+    <t>Hier werden Tageszeiten angegeben, zu denen das Arzneimittel verabreicht/eingenommen wird.
 Ergänzend können Zusatzinformationen angegeben werden, die die  Verabreichung/Einnahme des Arzneimittels in Bezug zu Mahlzeiten und Schlafzeiten abbilden.</t>
   </si>
   <si>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T11:53:44+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:53:44+01:00</t>
+    <t>2026-03-18T11:15:18+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T11:15:18+01:00</t>
+    <t>2026-03-18T12:55:48+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T12:55:48+01:00</t>
+    <t>2026-03-18T17:09:19+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-29T11:10:04+02:00</t>
+    <t>2026-06-24T16:51:19+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Hier werden Angaben dazu gemacht, wie ein bestimmtes Arzneimittel eingenommen bzw. verabreicht wird oder werden soll.</t>
+    <t>Diese Ressource bietet die Möglichkeit anzugeben, ob eine Medikation im System als Dauermedikation deklariert wurde.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -2369,7 +2369,7 @@
     <t>MedicationStatement.dosage.site.coding.display</t>
   </si>
   <si>
-    <t>Anatomical or acquired body structure</t>
+    <t>Anatomische oder erworbene Körperstruktur</t>
   </si>
   <si>
     <t>MedicationStatement.dosage.site.coding.userSelected</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:51:19+02:00</t>
+    <t>2026-06-26T18:38:01+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T18:38:01+02:00</t>
+    <t>2026-07-06T17:54:18+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T17:54:18+02:00</t>
+    <t>2026-07-22T15:49:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
+++ b/site/StructureDefinition-KBV-PR-WEST-MedicationStatement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T15:49:40+02:00</t>
+    <t>2026-07-22T16:29:56+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
